--- a/artfynd/A 35743-2024 artfynd.xlsx
+++ b/artfynd/A 35743-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120397622</v>
+        <v>120397362</v>
       </c>
       <c r="B2" t="n">
-        <v>96885</v>
+        <v>96891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,8 +708,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753184</v>
+        <v>753014</v>
       </c>
       <c r="R2" t="n">
-        <v>7098119</v>
+        <v>7098123</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,28 +777,28 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Sandbarrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karin Åkeby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
+          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120397362</v>
+        <v>120397622</v>
       </c>
       <c r="B3" t="n">
-        <v>96891</v>
+        <v>96885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,16 +828,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753014</v>
+        <v>753184</v>
       </c>
       <c r="R3" t="n">
-        <v>7098123</v>
+        <v>7098119</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,18 +889,18 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Sandbarrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Karin Åkeby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
+          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 35743-2024 artfynd.xlsx
+++ b/artfynd/A 35743-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120397362</v>
+        <v>120397339</v>
       </c>
       <c r="B2" t="n">
-        <v>96891</v>
+        <v>77926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753014</v>
+        <v>752546</v>
       </c>
       <c r="R2" t="n">
-        <v>7098123</v>
+        <v>7098267</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,28 +768,43 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Sandbarrskog</t>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Karin Åkeby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
+          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120397622</v>
+        <v>120397362</v>
       </c>
       <c r="B3" t="n">
-        <v>96885</v>
+        <v>96891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,16 +817,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -828,8 +834,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -839,13 +853,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753184</v>
+        <v>753014</v>
       </c>
       <c r="R3" t="n">
-        <v>7098119</v>
+        <v>7098123</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,25 +903,25 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Sandbarrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin Åkeby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
+          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120398028</v>
+        <v>120397622</v>
       </c>
       <c r="B4" t="n">
         <v>96885</v>
@@ -940,16 +954,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -959,13 +965,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753014</v>
+        <v>753184</v>
       </c>
       <c r="R4" t="n">
-        <v>7098123</v>
+        <v>7098119</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,25 +1013,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Karin Åkeby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
+          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120397339</v>
+        <v>120398028</v>
       </c>
       <c r="B5" t="n">
-        <v>77926</v>
+        <v>96885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,30 +1045,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752546</v>
+        <v>753014</v>
       </c>
       <c r="R5" t="n">
-        <v>7098267</v>
+        <v>7098123</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,35 +1133,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karin Åkeby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
+          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 35743-2024 artfynd.xlsx
+++ b/artfynd/A 35743-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120397339</v>
+        <v>120397362</v>
       </c>
       <c r="B2" t="n">
-        <v>77926</v>
+        <v>96891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752546</v>
+        <v>753014</v>
       </c>
       <c r="R2" t="n">
-        <v>7098267</v>
+        <v>7098123</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -768,43 +777,28 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Sandbarrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karin Åkeby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
+          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120397362</v>
+        <v>120397339</v>
       </c>
       <c r="B3" t="n">
-        <v>96891</v>
+        <v>77926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +807,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753014</v>
+        <v>752546</v>
       </c>
       <c r="R3" t="n">
-        <v>7098123</v>
+        <v>7098267</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,25 +888,40 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Sandbarrskog</t>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Karin Åkeby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
+          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120397622</v>
+        <v>120398028</v>
       </c>
       <c r="B4" t="n">
         <v>96885</v>
@@ -954,8 +954,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -965,13 +973,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753184</v>
+        <v>753014</v>
       </c>
       <c r="R4" t="n">
-        <v>7098119</v>
+        <v>7098123</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,27 +1021,22 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karin Åkeby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
+          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120398028</v>
+        <v>120397622</v>
       </c>
       <c r="B5" t="n">
         <v>96885</v>
@@ -1066,16 +1069,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1085,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753014</v>
+        <v>753184</v>
       </c>
       <c r="R5" t="n">
-        <v>7098123</v>
+        <v>7098119</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,15 +1128,20 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Karin Åkeby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
+          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 35743-2024 artfynd.xlsx
+++ b/artfynd/A 35743-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120397362</v>
+        <v>120397622</v>
       </c>
       <c r="B2" t="n">
-        <v>96891</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,16 +708,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753014</v>
+        <v>753184</v>
       </c>
       <c r="R2" t="n">
-        <v>7098123</v>
+        <v>7098119</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,28 +769,28 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Sandbarrskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Karin Åkeby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
+          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120397339</v>
+        <v>120397362</v>
       </c>
       <c r="B3" t="n">
-        <v>77926</v>
+        <v>96891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,30 +799,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752546</v>
+        <v>753014</v>
       </c>
       <c r="R3" t="n">
-        <v>7098267</v>
+        <v>7098123</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,43 +889,28 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Sandbarrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karin Åkeby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
+          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120398028</v>
+        <v>120397339</v>
       </c>
       <c r="B4" t="n">
-        <v>96885</v>
+        <v>77926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,39 +919,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753014</v>
+        <v>752546</v>
       </c>
       <c r="R4" t="n">
-        <v>7098123</v>
+        <v>7098267</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,22 +998,42 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Karin Åkeby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
+          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120397622</v>
+        <v>120398028</v>
       </c>
       <c r="B5" t="n">
         <v>96885</v>
@@ -1069,8 +1066,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1080,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753184</v>
+        <v>753014</v>
       </c>
       <c r="R5" t="n">
-        <v>7098119</v>
+        <v>7098123</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,20 +1133,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karin Åkeby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
+          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 35743-2024 artfynd.xlsx
+++ b/artfynd/A 35743-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120397362</v>
+        <v>120398028</v>
       </c>
       <c r="B3" t="n">
-        <v>96891</v>
+        <v>96885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -887,11 +887,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -907,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120397339</v>
+        <v>120397362</v>
       </c>
       <c r="B4" t="n">
-        <v>77926</v>
+        <v>96891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,30 +914,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,13 +954,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752546</v>
+        <v>753014</v>
       </c>
       <c r="R4" t="n">
-        <v>7098267</v>
+        <v>7098123</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,43 +1004,28 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Sandbarrskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karin Åkeby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
+          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120398028</v>
+        <v>120397339</v>
       </c>
       <c r="B5" t="n">
-        <v>96885</v>
+        <v>77926</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,39 +1034,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753014</v>
+        <v>752546</v>
       </c>
       <c r="R5" t="n">
-        <v>7098123</v>
+        <v>7098267</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,15 +1113,35 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Karin Åkeby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Wikdahl, Marie Ridoff, Karin Åkeby, Jenny Karlstam</t>
+          <t>Karin Åkeby, Jenny Karlstam, Maria Wikdahl, Marie Ridoff</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
